--- a/Assets/Document/云熹约定项目文档/11.配音文本/陈予宁配音文本.xlsx
+++ b/Assets/Document/云熹约定项目文档/11.配音文本/陈予宁配音文本.xlsx
@@ -29,36 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>角色分析：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>海关职业，性格严谨、正派，声音低沉醇厚，措辞严密，带着职业性的审视与戒备。在与女主的对话中，逐渐从拘谨、惊讶到柔和</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>157字</t>
   </si>
@@ -90,13 +61,13 @@
     <t>“原来是这样……你的观察很细致。”</t>
   </si>
   <si>
-    <t>声音比刚才低了一些，像是在消化某种迟来的确认。语气若有所思，带着被“看见”后的微微震动。“细致”二字说得轻而真诚。</t>
+    <t>声音比刚才低了一些，像是在消化某种迟来的确认。语气若有所思，带着被“看见”后的微微震动。</t>
   </si>
   <si>
     <t>“嗯，如果周末不用加班，通常会在这里打两个小时，保持手感。你也喜欢打球吗？或许下次可以一起。”</t>
   </si>
   <si>
-    <t>语气放松了许多，眼底的光柔和了几分。前半句是沉稳的陈述，后半句带着试探性的邀请，语速放慢，“可以一起”说得轻巧，不给对方压力。</t>
+    <t>语气放松了许多，前半句是沉稳的陈述，后半句带着试探性的邀请，语速放慢，“可以一起”说得轻巧，不给对方压力。</t>
   </si>
   <si>
     <t>“回见，路上小心。”</t>
@@ -127,19 +98,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -300,12 +265,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -316,7 +275,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,133 +631,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -809,19 +768,19 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1144,84 +1103,83 @@
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="56.25" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="25.5" spans="1:2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="2" ht="14.25"/>
+    <row r="3" ht="26.25" spans="1:2">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="26.25" spans="1:2">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" ht="37.5" spans="1:2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" ht="18.75" spans="1:2">
       <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" ht="18.75" spans="1:2">
       <c r="A6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" ht="37.5" spans="1:2">
       <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" ht="37.5" spans="1:2">
       <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" ht="37.5" spans="1:2">
       <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="10" ht="18.75" spans="1:2">
       <c r="A10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" ht="19.5" spans="1:2">
       <c r="A11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
